--- a/1. RAG/data/4_testing/range_of_k/RAG_eval_k=3.xlsx
+++ b/1. RAG/data/4_testing/range_of_k/RAG_eval_k=3.xlsx
@@ -548,35 +548,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>I don't have enough information to answer that.</t>
+          <t>According to the provided context, 2% of gay men in Germany reported experiencing discrimination in the past year when showing their ID or any official document that identifies their sex.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7288</v>
+        <v>0.7181</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.577</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>61.2</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="3">
@@ -590,7 +590,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>I don't have enough information to answer that.</t>
+          <t>According to the context provided, 18% of lesbian women in France report being "always open" about their LGBT identity at work, while 54% are "selectively open," and 28% choose to "hide" their LGBT identity. This suggests that a significant portion of lesbian women feel comfortable being selectively open, but there is still a notable percentage that feels the need to hide their identity.</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -606,19 +606,19 @@
         <v>0.6972</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="I3" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.222</v>
+        <v>0.238</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>0.867</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>61.2</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="4">
@@ -639,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7064</v>
+        <v>0.6657</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>8</v>
@@ -723,13 +723,13 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5742</v>
+        <v>0.5777</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8</v>
@@ -765,7 +765,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>0.667</v>
@@ -813,7 +813,7 @@
         <v>0.667</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5152</v>
+        <v>0.5099</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>8</v>
@@ -855,7 +855,7 @@
         <v>0.667</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6085</v>
+        <v>0.3296</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.182</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_b_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E2" s="2" t="b">
@@ -949,7 +949,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_b — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Gay? | Germany responses (Transgender): Yes: 39%, No: 55%, Don`t know: 6%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -967,15 +967,15 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E3" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E4" s="2" t="b">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1094,13 +1094,17 @@
       <c r="C8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1116,13 +1120,17 @@
       <c r="C9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1148,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E10" s="2" t="b">
@@ -1148,7 +1156,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1186,11 +1194,7 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
-        </is>
-      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="2" t="b">
         <v>1</v>
       </c>
@@ -1238,24 +1242,22 @@
       <c r="C14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1275,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E15" s="4" t="b">
@@ -1281,18 +1283,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1306,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E16" s="2" t="b">
@@ -1318,18 +1314,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -1377,11 +1367,7 @@
       <c r="C18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
-        </is>
-      </c>
+      <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="2" t="b">
         <v>1</v>
       </c>
@@ -1441,25 +1427,28 @@
       <c r="C20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1475,25 +1464,28 @@
       <c r="C21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E21" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1509,29 +1501,24 @@
       <c r="C22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -1553,19 +1540,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1558,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E24" s="2" t="b">
@@ -1591,19 +1566,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1584,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E25" s="4" t="b">
@@ -1629,19 +1592,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
